--- a/DATA/MODELADO/Bitacoras/Exp01/bitacora_maestra_experimentos.xlsx
+++ b/DATA/MODELADO/Bitacoras/Exp01/bitacora_maestra_experimentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,41 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Precision</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Recall</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>F1_Score</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Especificidad</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy_Balanceada</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Estado_General</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>Tiempo_Segundos</t>
         </is>
       </c>
@@ -566,7 +601,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46231.68066905859</v>
+        <v>46232.93431272278</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -622,28 +657,51 @@
         <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5449524521827698</v>
+        <v>0.008667116984724998</v>
       </c>
       <c r="T2" t="n">
-        <v>1.24668300151825</v>
+        <v>0.1848334670066833</v>
       </c>
       <c r="U2" t="n">
-        <v>1.591097950935364</v>
+        <v>0.9517776370048523</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9612188339233398</v>
+        <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8441558480262756</v>
+        <v>0.9220778942108154</v>
       </c>
       <c r="X2" t="n">
         <v>0.8461538553237915</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.65387725830078</v>
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>MODELO NO APTO PARA DETECTAR OBJETIVO</t>
+        </is>
+      </c>
+      <c r="AF2" t="n">
+        <v>12.17211174964905</v>
       </c>
     </row>
   </sheetData>

--- a/DATA/MODELADO/Bitacoras/Exp01/bitacora_maestra_experimentos.xlsx
+++ b/DATA/MODELADO/Bitacoras/Exp01/bitacora_maestra_experimentos.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>46232.93431272278</v>
+        <v>46245.6782171875</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -620,7 +620,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Escalado MinMax</t>
+          <t>RobustScaler</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -657,22 +657,22 @@
         <v>100</v>
       </c>
       <c r="R2" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="S2" t="n">
-        <v>0.008667116984724998</v>
+        <v>0.193439245223999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1848334670066833</v>
+        <v>1.017821669578552</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9517776370048523</v>
+        <v>1.15725576877594</v>
       </c>
       <c r="V2" t="n">
-        <v>1</v>
+        <v>0.9418282508850098</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9220778942108154</v>
+        <v>0.8441558480262756</v>
       </c>
       <c r="X2" t="n">
         <v>0.8461538553237915</v>
@@ -697,11 +697,121 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>MODELO NO APTO PARA DETECTAR OBJETIVO</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>12.17211174964905</v>
+        <v>5.749446392059326</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Exp01</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>46245.68250678573</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Gestión Hídrica</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>irca</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>LSTM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>RobustScaler</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>516</v>
+      </c>
+      <c r="J3" t="n">
+        <v>361</v>
+      </c>
+      <c r="K3" t="n">
+        <v>77</v>
+      </c>
+      <c r="L3" t="n">
+        <v>78</v>
+      </c>
+      <c r="M3" t="n">
+        <v>32</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="P3" t="n">
+        <v>32</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R3" t="n">
+        <v>31</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.02975934371352196</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.4987682402133942</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5281597971916199</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9944598078727722</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.8831169009208679</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8461538553237915</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Bueno</t>
+        </is>
+      </c>
+      <c r="AF3" t="n">
+        <v>17.90417981147766</v>
       </c>
     </row>
   </sheetData>
